--- a/Assets/Data/Dungeon1010.xlsx
+++ b/Assets/Data/Dungeon1010.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -52,10 +52,13 @@
     <t>□</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Out</t>
+  </si>
+  <si>
+    <t>Tr:D3</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -92,8 +95,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -111,6 +114,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -119,37 +145,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,45 +166,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,17 +174,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,7 +198,61 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,13 +267,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,43 +291,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -336,13 +315,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -354,13 +345,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -372,37 +411,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,31 +429,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,15 +458,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -482,17 +476,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -502,26 +505,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -541,17 +524,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,145 +566,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -781,19 +784,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1008,6 +1009,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3947,7 +3950,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>8</v>
@@ -5806,34 +5809,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11">
